--- a/DATA/production_capacity_scenarios/cap_builder.xlsx
+++ b/DATA/production_capacity_scenarios/cap_builder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D48793-44F8-4CA7-921C-D628B47986B8}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B21E7B9B-83EE-45A9-A8C1-6DA82B5FFF61}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="32770" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="36">
   <si>
     <t>Vaccine</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Predicted Capacity</t>
   </si>
   <si>
-    <t>DTwP-HepB-Hib</t>
-  </si>
-  <si>
     <t>Rota</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>TT</t>
   </si>
   <si>
-    <t>bOPV</t>
-  </si>
-  <si>
     <t>DT</t>
   </si>
   <si>
@@ -148,6 +142,9 @@
   </si>
   <si>
     <t>OPV</t>
+  </si>
+  <si>
+    <t>DTwP-Hib</t>
   </si>
 </sst>
 </file>
@@ -696,6 +693,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1015,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA7A5DA-6C9D-46FC-975A-A9F5DD878FF9}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1032,130 +1033,138 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>95748333.180000007</v>
+        <v>1554268.8119999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>100784999.40000001</v>
+        <v>61084402.119999997</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>1081708.747</v>
+        <v>2674099.1159999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>11549646.18</v>
+        <v>6977250.5789999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>78105242.920000002</v>
+        <v>366000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>1330887.28</v>
+        <v>1081708.747</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>38934732.43</v>
+        <v>64210185.420000002</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B9">
-        <v>6977250.5789999999</v>
+        <v>87000000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>109415283.90000001</v>
+        <v>38934732.43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>1192043.416</v>
+        <v>23500755.780000001</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12">
-        <v>8588942.9780000001</v>
+        <v>201758499.40000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>9948937.4529999997</v>
+        <v>347816361</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B14">
-        <v>98031755.310000002</v>
+        <v>148936259.09999999</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B15">
-        <v>87000000</v>
+        <v>196652183.90000001</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B16">
-        <v>59350830.350000001</v>
+        <v>138970173.69999999</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1">
-        <v>366000</v>
+        <v>188318801.59999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>11549646.18</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.5703125" bestFit="1" customWidth="1"/>
@@ -1187,10 +1196,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1198,156 +1207,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>0.352162617276225</v>
+        <v>0.61831770997823843</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B3">
-        <v>0.31873823734484802</v>
+        <v>0.38168229002176157</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B4">
-        <v>0.192155901226716</v>
+        <v>0.79401392160994866</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>0.13694324415220899</v>
+        <v>0.20598607839005142</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>0.52512572032754001</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>0.47487427967245899</v>
+        <v>0.52512572032754001</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>0.79401392160994866</v>
+        <v>0.47487427967245899</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>0.20598607839005142</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B10">
-        <v>0.56344220359613195</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
-        <v>0.407494488007414</v>
+        <v>0.88757027197187544</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>2.9063308396452301E-2</v>
+        <v>7.5820864829665865E-2</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>0.39454798551666598</v>
+        <v>3.6608863198458602E-2</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>0.23280346724176701</v>
+        <v>0.74287578329988224</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>0.165439934217085</v>
+        <v>0.13848452188328597</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1355,29 +1364,29 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>7.9812538359880295E-2</v>
+        <v>3.0007480916812632E-2</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>6.4497366297362302E-2</v>
+        <v>8.8632213900019075E-2</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>3.0077883934385902E-2</v>
+        <v>0.84733915633184897</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -1385,10 +1394,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>3.00746331444584E-2</v>
+        <v>0.15266084366815</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
@@ -1399,241 +1408,241 @@
         <v>32</v>
       </c>
       <c r="B20">
-        <v>2.7461912883932999E-3</v>
+        <v>0.73266544221843499</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B21">
-        <v>0.73266544221843499</v>
+        <v>0.26733455778156401</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>0.26733455778156401</v>
+        <v>0.841178437394558</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B23">
-        <v>0.88757027197187544</v>
+        <v>0.158821562605441</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B24">
-        <v>7.5820864829665865E-2</v>
+        <v>0.39454798551666598</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B25">
-        <v>3.6608863198458602E-2</v>
+        <v>0.23280346724176701</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>0.165439934217085</v>
+      </c>
+      <c r="C26" t="s">
         <v>34</v>
-      </c>
-      <c r="B26">
-        <v>0.841178437394558</v>
-      </c>
-      <c r="C26" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>0.158821562605441</v>
+        <v>7.9812538359880295E-2</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>6.4497366297362302E-2</v>
+      </c>
+      <c r="C28" t="s">
         <v>34</v>
-      </c>
-      <c r="B28">
-        <v>0.50508041868836795</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B29">
-        <v>0.23963301566776399</v>
+        <v>3.0077883934385902E-2</v>
       </c>
       <c r="C29" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
-        <v>0.19210678946315199</v>
+        <v>3.00746331444584E-2</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>5.0439283720812897E-2</v>
+        <v>2.7461912883932999E-3</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B32">
-        <v>1.2740492459903101E-2</v>
+        <v>0.56344220359613195</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B33">
-        <v>0.45420990015180701</v>
+        <v>0.407494488007414</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>0.28037992773423698</v>
+        <v>2.9063308396452301E-2</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>0.26541017211395501</v>
+        <v>0.50508041868836795</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>0.590178760593704</v>
+        <v>0.23963301566776399</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B37">
-        <v>0.17977648197656701</v>
+        <v>0.19210678946315199</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B38">
-        <v>0.176380568497469</v>
+        <v>5.0439283720812897E-2</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39">
+        <v>1.2740492459903101E-2</v>
+      </c>
+      <c r="C39" t="s">
         <v>33</v>
-      </c>
-      <c r="B39">
-        <v>5.3664188932258203E-2</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B40">
-        <v>0.76585722949907797</v>
+        <v>0.91502251799193601</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B41">
-        <v>0.14276864940585099</v>
+        <v>5.9890161501362497E-2</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1641,87 +1650,98 @@
         <v>23</v>
       </c>
       <c r="B42">
-        <v>9.1374121095069802E-2</v>
+        <v>2.5087320506701101E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0.352162617276225</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B44">
-        <v>0.91502251799193601</v>
+        <v>0.31873823734484802</v>
       </c>
       <c r="C44" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B45">
-        <v>5.9890161501362497E-2</v>
+        <v>0.192155901226716</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B46">
-        <v>2.5087320506701101E-2</v>
+        <v>0.13694324415220899</v>
       </c>
       <c r="C46" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B47">
-        <v>0.84733915633184897</v>
+        <v>0.590178760593704</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B48">
-        <v>0.15266084366815</v>
+        <v>0.17977648197656701</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>0.176380568497469</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50">
+        <v>5.3664188932258203E-2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/production_capacity_scenarios/cap_builder.xlsx
+++ b/DATA/production_capacity_scenarios/cap_builder.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B21E7B9B-83EE-45A9-A8C1-6DA82B5FFF61}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BE10BB0-72FC-4F9B-81D1-EA651906DAA0}"/>
   <bookViews>
-    <workbookView xWindow="32770" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
     <sheet name="prop_by_manuf" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$C$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1174,6 +1174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1205,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1249,7 +1250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1260,7 +1261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1271,7 +1272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1282,7 +1283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1293,7 +1294,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1304,7 +1305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1326,7 +1327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1381,7 +1382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1392,7 +1393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1414,7 +1415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1425,7 +1426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1447,7 +1448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1469,7 +1470,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1480,7 +1481,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -1502,7 +1503,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1524,7 +1525,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1535,7 +1536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -1557,7 +1558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1579,7 +1580,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -1601,7 +1602,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -1612,7 +1613,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -1678,7 +1679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>31</v>
       </c>
@@ -1700,7 +1701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1711,7 +1712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -1722,7 +1723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -1733,7 +1734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>31</v>
       </c>
@@ -1745,7 +1746,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C49" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}"/>
+  <autoFilter ref="A1:C50" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="IPV"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA/production_capacity_scenarios/cap_builder.xlsx
+++ b/DATA/production_capacity_scenarios/cap_builder.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BE10BB0-72FC-4F9B-81D1-EA651906DAA0}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DEBD7B-E1EA-429F-99E8-075FD2269C18}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
     <sheet name="prop_by_manuf" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$C$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
   <si>
     <t>Vaccine</t>
   </si>
@@ -145,6 +145,21 @@
   </si>
   <si>
     <t>DTwP-Hib</t>
+  </si>
+  <si>
+    <t>Starting Cap</t>
+  </si>
+  <si>
+    <t>Cap by ratio</t>
+  </si>
+  <si>
+    <t>Scenario adjustment</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Totals</t>
   </si>
 </sst>
 </file>
@@ -291,7 +306,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +484,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -633,9 +654,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1174,28 +1197,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1205,8 +1231,23 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1216,8 +1257,23 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <f>VLOOKUP(C2,starting_cap!$A$2:$B$19,2)</f>
+        <v>1554268.8119999999</v>
+      </c>
+      <c r="E2">
+        <f>D2*B2</f>
+        <v>961031.9325264371</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF(A:A, I2, E:E)</f>
+        <v>7711002.6093016593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1227,8 +1283,23 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <f>VLOOKUP(C3,starting_cap!$A$2:$B$19,2)</f>
+        <v>1554268.8119999999</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E50" si="0">D3*B3</f>
+        <v>593236.87947356282</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3">
+        <f>SUMIF(A:A, I3, E:E)</f>
+        <v>39223955.730224065</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1238,8 +1309,23 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f>VLOOKUP(C4,starting_cap!$A$2:$B$19,2)</f>
+        <v>61084402.119999997</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>48501865.676500261</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF(A:A, I4, E:E)</f>
+        <v>61029105.171949707</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1249,8 +1335,23 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <f>VLOOKUP(C5,starting_cap!$A$2:$B$19,2)</f>
+        <v>61084402.119999997</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>12582536.443499742</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <f>SUMIF(A:A, I5, E:E)</f>
+        <v>12048153.40384588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1260,8 +1361,23 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f>VLOOKUP(C6,starting_cap!$A$2:$B$19,2)</f>
+        <v>2674099.1159999999</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>2674099.1159999999</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF(A:A, I6, E:E)</f>
+        <v>164885690.37433171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1271,8 +1387,23 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <f>VLOOKUP(C7,starting_cap!$A$2:$B$19,2)</f>
+        <v>6977250.5789999999</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>3663933.7362031206</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7">
+        <f>SUMIF(A:A, I7, E:E)</f>
+        <v>12812242.030626908</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1282,8 +1413,23 @@
       <c r="C8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <f>VLOOKUP(C8,starting_cap!$A$2:$B$19,2)</f>
+        <v>6977250.5789999999</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>3313316.8427968724</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8">
+        <f>SUMIF(A:A, I8, E:E)</f>
+        <v>226762685.51034766</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1293,8 +1439,23 @@
       <c r="C9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <f>VLOOKUP(C9,starting_cap!$A$2:$B$19,2)</f>
+        <v>366000</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>366000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <f>SUMIF(A:A, I9, E:E)</f>
+        <v>80972854.804214105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1304,8 +1465,23 @@
       <c r="C10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <f>VLOOKUP(C10,starting_cap!$A$2:$B$19,2)</f>
+        <v>1081708.747</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1081708.747</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10">
+        <f>SUMIF(A:A, I10, E:E)</f>
+        <v>43702187.372505918</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1315,8 +1491,23 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <f>VLOOKUP(C11,starting_cap!$A$2:$B$19,2)</f>
+        <v>64210185.420000002</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>56991051.736593954</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11">
+        <f>SUMIF(A:A, I11, E:E)</f>
+        <v>56991051.736593954</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1326,8 +1517,23 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <f>VLOOKUP(C12,starting_cap!$A$2:$B$19,2)</f>
+        <v>64210185.420000002</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>4868471.7894176021</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12">
+        <f>SUMIF(A:A, I12, E:E)</f>
+        <v>10874165.558588434</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1337,8 +1543,23 @@
       <c r="C13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <f>VLOOKUP(C13,starting_cap!$A$2:$B$19,2)</f>
+        <v>64210185.420000002</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>2350661.8939884412</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <f>SUMIF(A:A, I13, E:E)</f>
+        <v>83916974.022668451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1348,8 +1569,23 @@
       <c r="C14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <f>VLOOKUP(C14,starting_cap!$A$2:$B$19,2)</f>
+        <v>87000000</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>64630193.147089757</v>
+      </c>
+      <c r="I14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14">
+        <f>SUMIF(A:A, I14, E:E)</f>
+        <v>45911731.125812441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1359,8 +1595,23 @@
       <c r="C15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f>VLOOKUP(C15,starting_cap!$A$2:$B$19,2)</f>
+        <v>87000000</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>12048153.40384588</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15">
+        <f>SUMIF(A:A, I15, E:E)</f>
+        <v>87429432.386722356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1370,8 +1621,23 @@
       <c r="C16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <f>VLOOKUP(C16,starting_cap!$A$2:$B$19,2)</f>
+        <v>87000000</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>2610650.8397626989</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16">
+        <f>SUMIF(A:A, I16, E:E)</f>
+        <v>587114096.04626513</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1381,8 +1647,16 @@
       <c r="C17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <f>VLOOKUP(C17,starting_cap!$A$2:$B$19,2)</f>
+        <v>87000000</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>7711002.6093016593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1392,8 +1666,16 @@
       <c r="C18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <f>VLOOKUP(C18,starting_cap!$A$2:$B$19,2)</f>
+        <v>38934732.43</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>32990923.329242479</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1403,8 +1685,16 @@
       <c r="C19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <f>VLOOKUP(C19,starting_cap!$A$2:$B$19,2)</f>
+        <v>38934732.43</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>5943809.1007574797</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1414,8 +1704,16 @@
       <c r="C20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <f>VLOOKUP(C20,starting_cap!$A$2:$B$19,2)</f>
+        <v>23500755.780000001</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>17218191.626021143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1425,8 +1723,16 @@
       <c r="C21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <f>VLOOKUP(C21,starting_cap!$A$2:$B$19,2)</f>
+        <v>23500755.780000001</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>6282564.1539788349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1436,8 +1742,16 @@
       <c r="C22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <f>VLOOKUP(C22,starting_cap!$A$2:$B$19,2)</f>
+        <v>201758499.40000001</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>169714899.25636289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1447,8 +1761,16 @@
       <c r="C23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <f>VLOOKUP(C23,starting_cap!$A$2:$B$19,2)</f>
+        <v>201758499.40000001</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>32043600.143636931</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1780,16 @@
       <c r="C24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <f>VLOOKUP(C24,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>137230244.56228748</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1469,8 +1799,16 @@
       <c r="C25" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <f>VLOOKUP(C25,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>80972854.804214105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1480,8 +1818,16 @@
       <c r="C26" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <f>VLOOKUP(C26,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>57542715.883465886</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1491,8 +1837,16 @@
       <c r="C27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <f>VLOOKUP(C27,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>27760106.654506471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -1502,8 +1856,16 @@
       <c r="C28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <f>VLOOKUP(C28,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>22433239.239632599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1513,8 +1875,16 @@
       <c r="C29" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <f>VLOOKUP(C29,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>10461580.136638466</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1524,8 +1894,16 @@
       <c r="C30" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <f>VLOOKUP(C30,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>10460449.458715508</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1535,8 +1913,16 @@
       <c r="C31" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <f>VLOOKUP(C31,starting_cap!$A$2:$B$19,2)</f>
+        <v>347816361</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>955170.26053885918</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1546,8 +1932,16 @@
       <c r="C32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <f>VLOOKUP(C32,starting_cap!$A$2:$B$19,2)</f>
+        <v>148936259.09999999</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>83916974.022668451</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -1557,8 +1951,16 @@
       <c r="C33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <f>VLOOKUP(C33,starting_cap!$A$2:$B$19,2)</f>
+        <v>148936259.09999999</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>60690704.647694051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1568,8 +1970,16 @@
       <c r="C34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <f>VLOOKUP(C34,starting_cap!$A$2:$B$19,2)</f>
+        <v>148936259.09999999</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="0"/>
+        <v>4328580.4296372253</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1579,8 +1989,16 @@
       <c r="C35" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <f>VLOOKUP(C35,starting_cap!$A$2:$B$19,2)</f>
+        <v>196652183.90000001</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>99325167.380193934</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +2008,16 @@
       <c r="C36" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <f>VLOOKUP(C36,starting_cap!$A$2:$B$19,2)</f>
+        <v>196652183.90000001</v>
+      </c>
+      <c r="E36">
+        <f>D36*B36</f>
+        <v>47124355.865608707</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -1601,8 +2027,16 @@
       <c r="C37" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <f>VLOOKUP(C37,starting_cap!$A$2:$B$19,2)</f>
+        <v>196652183.90000001</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>37778219.689946346</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -1612,8 +2046,16 @@
       <c r="C38" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <f>VLOOKUP(C38,starting_cap!$A$2:$B$19,2)</f>
+        <v>196652183.90000001</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="0"/>
+        <v>9918995.2980495747</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -1623,8 +2065,16 @@
       <c r="C39" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <f>VLOOKUP(C39,starting_cap!$A$2:$B$19,2)</f>
+        <v>196652183.90000001</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>2505445.666201428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +2084,16 @@
       <c r="C40" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <f>VLOOKUP(C40,starting_cap!$A$2:$B$19,2)</f>
+        <v>138970173.69999999</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>127160838.26475072</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -1645,8 +2103,16 @@
       <c r="C41" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <f>VLOOKUP(C41,starting_cap!$A$2:$B$19,2)</f>
+        <v>138970173.69999999</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>8322946.1467653988</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1656,8 +2122,16 @@
       <c r="C42" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <f>VLOOKUP(C42,starting_cap!$A$2:$B$19,2)</f>
+        <v>138970173.69999999</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="0"/>
+        <v>3486389.2884838236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -1667,8 +2141,16 @@
       <c r="C43" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <f>VLOOKUP(C43,starting_cap!$A$2:$B$19,2)</f>
+        <v>188318801.59999999</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>66318842.053778149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -1678,8 +2160,16 @@
       <c r="C44" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <f>VLOOKUP(C44,starting_cap!$A$2:$B$19,2)</f>
+        <v>188318801.59999999</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>60024402.880878143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -1689,8 +2179,16 @@
       <c r="C45" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <f>VLOOKUP(C45,starting_cap!$A$2:$B$19,2)</f>
+        <v>188318801.59999999</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>36186569.039383128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>31</v>
       </c>
@@ -1700,8 +2198,16 @@
       <c r="C46" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <f>VLOOKUP(C46,starting_cap!$A$2:$B$19,2)</f>
+        <v>188318801.59999999</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="0"/>
+        <v>25788987.625960205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1711,8 +2217,16 @@
       <c r="C47" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <f>VLOOKUP(C47,starting_cap!$A$2:$B$19,2)</f>
+        <v>11549646.18</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>6816355.8678082079</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -1722,8 +2236,16 @@
       <c r="C48" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <f>VLOOKUP(C48,starting_cap!$A$2:$B$19,2)</f>
+        <v>11549646.18</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>2076354.7583144959</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -1733,8 +2255,16 @@
       <c r="C49" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <f>VLOOKUP(C49,starting_cap!$A$2:$B$19,2)</f>
+        <v>11549646.18</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>2037133.1591730211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>31</v>
       </c>
@@ -1744,15 +2274,17 @@
       <c r="C50" t="s">
         <v>4</v>
       </c>
+      <c r="D50">
+        <f>VLOOKUP(C50,starting_cap!$A$2:$B$19,2)</f>
+        <v>11549646.18</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>619802.39470425423</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C50" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="IPV"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E51" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA/production_capacity_scenarios/cap_builder.xlsx
+++ b/DATA/production_capacity_scenarios/cap_builder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DEBD7B-E1EA-429F-99E8-075FD2269C18}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF4F9CE-542A-4F7A-9DCD-734FC4397F51}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="prop_by_manuf" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">prop_by_manuf!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,20 +37,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="40">
   <si>
     <t>Vaccine</t>
   </si>
   <si>
-    <t>Predicted Capacity</t>
-  </si>
-  <si>
     <t>Rota</t>
   </si>
   <si>
-    <t>Hib</t>
-  </si>
-  <si>
     <t>TT</t>
   </si>
   <si>
@@ -60,9 +54,6 @@
     <t>Measles</t>
   </si>
   <si>
-    <t>HepB</t>
-  </si>
-  <si>
     <t>PCV</t>
   </si>
   <si>
@@ -160,16 +151,18 @@
   </si>
   <si>
     <t>Totals</t>
+  </si>
+  <si>
+    <t>Hep_B</t>
+  </si>
+  <si>
+    <t>Predicted Demand</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -306,7 +299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,12 +477,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -609,7 +596,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -652,15 +639,11 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -688,7 +671,6 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1039,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA7A5DA-6C9D-46FC-975A-A9F5DD878FF9}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1051,143 +1033,135 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>1554268.8119999999</v>
+        <v>977251.31527214276</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>61084402.119999997</v>
+        <v>13328055.520714156</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>2674099.1159999999</v>
+        <v>321326687.20403224</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>6977250.5789999999</v>
+        <v>6402511.719496578</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>366000</v>
+        <v>59151603.417757481</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>1081708.747</v>
+        <v>277874999.07853091</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>64210185.420000002</v>
+        <v>302888.81815348461</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>87000000</v>
+        <v>6311801.7126107905</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>38934732.43</v>
+        <v>66709612.957940787</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>23500755.780000001</v>
+        <v>136545787.17132425</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B12">
-        <v>201758499.40000001</v>
+        <v>266622339.29579192</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>347816361</v>
+        <v>3172885.866301666</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B14">
-        <v>148936259.09999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B15">
-        <v>196652183.90000001</v>
+        <v>35984585.712862946</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16">
-        <v>138970173.69999999</v>
+        <v>217521514.44316691</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="1">
-        <v>188318801.59999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18">
-        <v>11549646.18</v>
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>226180575.91757733</v>
       </c>
     </row>
   </sheetData>
@@ -1197,14 +1171,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
@@ -1223,589 +1197,589 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>37</v>
-      </c>
-      <c r="F1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>0.61831770997823843</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <f>VLOOKUP(C2,starting_cap!$A$2:$B$19,2)</f>
-        <v>1554268.8119999999</v>
+        <f>VLOOKUP(C2,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>6402511.719496578</v>
       </c>
       <c r="E2">
-        <f>D2*B2</f>
-        <v>961031.9325264371</v>
+        <f t="shared" ref="E2:E49" si="0">D2*B2</f>
+        <v>3958786.3845079578</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <f>SUMIF(A:A, I2, E:E)</f>
-        <v>7711002.6093016593</v>
+        <f t="shared" ref="J2:J16" si="1">SUMIF(A:A, I2, E:E)</f>
+        <v>12102355.415715292</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>0.38168229002176157</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <f>VLOOKUP(C3,starting_cap!$A$2:$B$19,2)</f>
-        <v>1554268.8119999999</v>
+        <f>VLOOKUP(C3,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>6402511.719496578</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E50" si="0">D3*B3</f>
-        <v>593236.87947356282</v>
+        <f t="shared" si="0"/>
+        <v>2443725.3349886201</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <f>SUMIF(A:A, I3, E:E)</f>
-        <v>39223955.730224065</v>
+        <f t="shared" si="1"/>
+        <v>55762252.537822999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0.79401392160994866</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <f>VLOOKUP(C4,starting_cap!$A$2:$B$19,2)</f>
-        <v>61084402.119999997</v>
+        <f>VLOOKUP(C4,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>59151603.417757481</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>48501865.676500261</v>
+        <v>46967196.599250063</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J4">
-        <f>SUMIF(A:A, I4, E:E)</f>
-        <v>61029105.171949707</v>
+        <f t="shared" si="1"/>
+        <v>5457031.9499387406</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.20598607839005142</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <f>VLOOKUP(C5,starting_cap!$A$2:$B$19,2)</f>
-        <v>61084402.119999997</v>
+        <f>VLOOKUP(C5,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>59151603.417757481</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>12582536.443499742</v>
+        <v>12184406.818507425</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J5">
-        <f>SUMIF(A:A, I5, E:E)</f>
-        <v>12048153.40384588</v>
+        <f t="shared" si="1"/>
+        <v>18909478.051597763</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <f>VLOOKUP(C6,starting_cap!$A$2:$B$19,2)</f>
-        <v>2674099.1159999999</v>
+        <f>VLOOKUP(C6,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>6311801.7126107905</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>2674099.1159999999</v>
+        <v>6311801.7126107905</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <f>SUMIF(A:A, I6, E:E)</f>
-        <v>164885690.37433171</v>
+        <f t="shared" si="1"/>
+        <v>176656204.10945982</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>0.52512572032754001</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <f>VLOOKUP(C7,starting_cap!$A$2:$B$19,2)</f>
-        <v>6977250.5789999999</v>
+        <f>VLOOKUP(C7,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>66709612.957940787</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>3663933.7362031206</v>
+        <v>35030933.557310052</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J7">
-        <f>SUMIF(A:A, I7, E:E)</f>
-        <v>12812242.030626908</v>
+        <f t="shared" si="1"/>
+        <v>1317354.7756154076</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>0.47487427967245899</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D8">
-        <f>VLOOKUP(C8,starting_cap!$A$2:$B$19,2)</f>
-        <v>6977250.5789999999</v>
+        <f>VLOOKUP(C8,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>66709612.957940787</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>3313316.8427968724</v>
+        <v>31678679.400630668</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <f>SUMIF(A:A, I8, E:E)</f>
-        <v>226762685.51034766</v>
+        <f t="shared" si="1"/>
+        <v>379834532.08035249</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <f>VLOOKUP(C9,starting_cap!$A$2:$B$19,2)</f>
-        <v>366000</v>
+        <f>VLOOKUP(C9,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>302888.81815348461</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>366000</v>
+        <v>302888.81815348461</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <f>SUMIF(A:A, I9, E:E)</f>
-        <v>80972854.804214105</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0.88757027197187544</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <f>VLOOKUP(C10,starting_cap!$A$2:$B$19,2)</f>
-        <v>1081708.747</v>
+        <f>VLOOKUP(C10,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>35984585.712862946</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1081708.747</v>
+        <v>31938848.527961027</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J10">
-        <f>SUMIF(A:A, I10, E:E)</f>
-        <v>43702187.372505918</v>
+        <f t="shared" si="1"/>
+        <v>89157748.448498234</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B11">
-        <v>0.88757027197187544</v>
+        <v>7.5820864829665865E-2</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <f>VLOOKUP(C11,starting_cap!$A$2:$B$19,2)</f>
-        <v>64210185.420000002</v>
+        <f>VLOOKUP(C11,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>35984585.712862946</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>56991051.736593954</v>
+        <v>2728382.4092865069</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J11">
-        <f>SUMIF(A:A, I11, E:E)</f>
-        <v>56991051.736593954</v>
+        <f t="shared" si="1"/>
+        <v>31938848.527961027</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>7.5820864829665865E-2</v>
+        <v>3.6608863198458602E-2</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <f>VLOOKUP(C12,starting_cap!$A$2:$B$19,2)</f>
-        <v>64210185.420000002</v>
+        <f>VLOOKUP(C12,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>35984585.712862946</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>4868471.7894176021</v>
+        <v>1317354.7756154076</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J12">
-        <f>SUMIF(A:A, I12, E:E)</f>
-        <v>10874165.558588434</v>
+        <f t="shared" si="1"/>
+        <v>14015815.917442642</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>3.6608863198458602E-2</v>
+        <v>0.74287578329988224</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <f>VLOOKUP(C13,starting_cap!$A$2:$B$19,2)</f>
-        <v>64210185.420000002</v>
+        <f>VLOOKUP(C13,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>136545787.17132425</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>2350661.8939884412</v>
+        <v>101436558.60119651</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <f>SUMIF(A:A, I13, E:E)</f>
-        <v>83916974.022668451</v>
+        <f t="shared" si="1"/>
+        <v>127439682.10564198</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>0.74287578329988224</v>
+        <v>0.13848452188328597</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <f>VLOOKUP(C14,starting_cap!$A$2:$B$19,2)</f>
-        <v>87000000</v>
+        <f>VLOOKUP(C14,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>136545787.17132425</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>64630193.147089757</v>
+        <v>18909478.051597763</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J14">
-        <f>SUMIF(A:A, I14, E:E)</f>
-        <v>45911731.125812441</v>
+        <f t="shared" si="1"/>
+        <v>42815576.129015923</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>0.13848452188328597</v>
+        <v>3.0007480916812632E-2</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <f>VLOOKUP(C15,starting_cap!$A$2:$B$19,2)</f>
-        <v>87000000</v>
+        <f>VLOOKUP(C15,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>136545787.17132425</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
-        <v>12048153.40384588</v>
+        <v>4097395.1028146716</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J15">
-        <f>SUMIF(A:A, I15, E:E)</f>
-        <v>87429432.386722356</v>
+        <f t="shared" si="1"/>
+        <v>101739447.41935</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>3.0007480916812632E-2</v>
+        <v>8.8632213900019075E-2</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <f>VLOOKUP(C16,starting_cap!$A$2:$B$19,2)</f>
-        <v>87000000</v>
+        <f>VLOOKUP(C16,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>136545787.17132425</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
-        <v>2610650.8397626989</v>
+        <v>12102355.415715292</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J16">
-        <f>SUMIF(A:A, I16, E:E)</f>
-        <v>587114096.04626513</v>
+        <f t="shared" si="1"/>
+        <v>581266772.68311989</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>8.8632213900019075E-2</v>
+        <v>0.84733915633184897</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <f>VLOOKUP(C17,starting_cap!$A$2:$B$19,2)</f>
-        <v>87000000</v>
+        <f>VLOOKUP(C17,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>977251.31527214276</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
-        <v>7711002.6093016593</v>
+        <v>828063.30500688718</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B18">
-        <v>0.84733915633184897</v>
+        <v>0.15266084366815</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <f>VLOOKUP(C18,starting_cap!$A$2:$B$19,2)</f>
-        <v>38934732.43</v>
+        <f>VLOOKUP(C18,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>977251.31527214276</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>32990923.329242479</v>
+        <v>149188.01026525456</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>0.15266084366815</v>
+        <v>0.73266544221843499</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
       </c>
       <c r="D19">
-        <f>VLOOKUP(C19,starting_cap!$A$2:$B$19,2)</f>
-        <v>38934732.43</v>
+        <f>VLOOKUP(C19,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>321326687.20403224</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>5943809.1007574797</v>
+        <v>235424959.37692702</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>0.73266544221843499</v>
+        <v>0.26733455778156401</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <f>VLOOKUP(C20,starting_cap!$A$2:$B$19,2)</f>
-        <v>23500755.780000001</v>
+        <f>VLOOKUP(C20,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>321326687.20403224</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
-        <v>17218191.626021143</v>
+        <v>85901727.827104896</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21">
-        <v>0.26733455778156401</v>
+        <v>0.841178437394558</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <f>VLOOKUP(C21,starting_cap!$A$2:$B$19,2)</f>
-        <v>23500755.780000001</v>
+        <f>VLOOKUP(C21,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>13328055.520714156</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>6282564.1539788349</v>
+        <v>11211272.916422246</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>0.841178437394558</v>
+        <v>0.158821562605441</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <f>VLOOKUP(C22,starting_cap!$A$2:$B$19,2)</f>
-        <v>201758499.40000001</v>
+        <f>VLOOKUP(C22,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>13328055.520714156</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>169714899.25636289</v>
+        <v>2116782.6042918968</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B23">
-        <v>0.158821562605441</v>
+        <v>0.39454798551666598</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D23">
-        <f>VLOOKUP(C23,starting_cap!$A$2:$B$19,2)</f>
-        <v>201758499.40000001</v>
+        <f>VLOOKUP(C23,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>32043600.143636931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>0.39454798551666598</v>
+        <v>0.23280346724176701</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D24">
-        <f>VLOOKUP(C24,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C24,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
-        <v>137230244.56228748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B25">
-        <v>0.23280346724176701</v>
+        <v>0.165439934217085</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D25">
-        <f>VLOOKUP(C25,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C25,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
-        <v>80972854.804214105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1813,189 +1787,189 @@
         <v>23</v>
       </c>
       <c r="B26">
-        <v>0.165439934217085</v>
+        <v>7.9812538359880295E-2</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D26">
-        <f>VLOOKUP(C26,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C26,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E26">
         <f t="shared" si="0"/>
-        <v>57542715.883465886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B27">
-        <v>7.9812538359880295E-2</v>
+        <v>6.4497366297362302E-2</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D27">
-        <f>VLOOKUP(C27,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C27,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E27">
         <f t="shared" si="0"/>
-        <v>27760106.654506471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28">
-        <v>6.4497366297362302E-2</v>
+        <v>3.0077883934385902E-2</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <f>VLOOKUP(C28,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C28,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E28">
         <f t="shared" si="0"/>
-        <v>22433239.239632599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>3.0077883934385902E-2</v>
+        <v>3.00746331444584E-2</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D29">
-        <f>VLOOKUP(C29,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C29,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E29">
         <f t="shared" si="0"/>
-        <v>10461580.136638466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>2.7461912883932999E-3</v>
+      </c>
+      <c r="C30" t="s">
         <v>31</v>
       </c>
-      <c r="B30">
-        <v>3.00746331444584E-2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
       <c r="D30">
-        <f>VLOOKUP(C30,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
+        <f>VLOOKUP(C30,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="E30">
         <f t="shared" si="0"/>
-        <v>10460449.458715508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B31">
-        <v>2.7461912883932999E-3</v>
+        <v>0.56344220359613195</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <f>VLOOKUP(C31,starting_cap!$A$2:$B$19,2)</f>
-        <v>347816361</v>
-      </c>
-      <c r="E31" s="2">
-        <f t="shared" si="0"/>
-        <v>955170.26053885918</v>
+        <f>VLOOKUP(C31,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>226180575.91757733</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>127439682.10564198</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B32">
-        <v>0.56344220359613195</v>
+        <v>0.407494488007414</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <f>VLOOKUP(C32,starting_cap!$A$2:$B$19,2)</f>
-        <v>148936259.09999999</v>
+        <f>VLOOKUP(C32,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>226180575.91757733</v>
       </c>
       <c r="E32">
         <f t="shared" si="0"/>
-        <v>83916974.022668451</v>
+        <v>92167337.98075521</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B33">
-        <v>0.407494488007414</v>
+        <v>2.9063308396452301E-2</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <f>VLOOKUP(C33,starting_cap!$A$2:$B$19,2)</f>
-        <v>148936259.09999999</v>
+        <f>VLOOKUP(C33,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>226180575.91757733</v>
       </c>
       <c r="E33">
         <f t="shared" si="0"/>
-        <v>60690704.647694051</v>
+        <v>6573555.8311797418</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B34">
-        <v>2.9063308396452301E-2</v>
+        <v>0.50508041868836795</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D34">
-        <f>VLOOKUP(C34,starting_cap!$A$2:$B$19,2)</f>
-        <v>148936259.09999999</v>
+        <f>VLOOKUP(C34,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>277874999.07853091</v>
       </c>
       <c r="E34">
         <f t="shared" si="0"/>
-        <v>4328580.4296372253</v>
+        <v>140349220.87761426</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B35">
-        <v>0.50508041868836795</v>
+        <v>0.23963301566776399</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D35">
-        <f>VLOOKUP(C35,starting_cap!$A$2:$B$19,2)</f>
-        <v>196652183.90000001</v>
+        <f>VLOOKUP(C35,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>277874999.07853091</v>
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
-        <v>99325167.380193934</v>
+        <v>66588024.007865503</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2003,288 +1977,269 @@
         <v>25</v>
       </c>
       <c r="B36">
-        <v>0.23963301566776399</v>
+        <v>0.19210678946315199</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <f>VLOOKUP(C36,starting_cap!$A$2:$B$19,2)</f>
-        <v>196652183.90000001</v>
+        <f>VLOOKUP(C36,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>277874999.07853091</v>
       </c>
       <c r="E36">
-        <f>D36*B36</f>
-        <v>47124355.865608707</v>
+        <f t="shared" si="0"/>
+        <v>53381673.945052892</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>0.19210678946315199</v>
+        <v>5.0439283720812897E-2</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <f>VLOOKUP(C37,starting_cap!$A$2:$B$19,2)</f>
-        <v>196652183.90000001</v>
+        <f>VLOOKUP(C37,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>277874999.07853091</v>
       </c>
       <c r="E37">
         <f t="shared" si="0"/>
-        <v>37778219.689946346</v>
+        <v>14015815.917442642</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38">
+        <v>1.2740492459903101E-2</v>
+      </c>
+      <c r="C38" t="s">
         <v>30</v>
       </c>
-      <c r="B38">
-        <v>5.0439283720812897E-2</v>
-      </c>
-      <c r="C38" t="s">
-        <v>33</v>
-      </c>
       <c r="D38">
-        <f>VLOOKUP(C38,starting_cap!$A$2:$B$19,2)</f>
-        <v>196652183.90000001</v>
-      </c>
-      <c r="E38" s="3">
-        <f t="shared" si="0"/>
-        <v>9918995.2980495747</v>
+        <f>VLOOKUP(C38,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>277874999.07853091</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="0"/>
+        <v>3540264.3305556043</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B39">
-        <v>1.2740492459903101E-2</v>
+        <v>0.91502251799193601</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <f>VLOOKUP(C39,starting_cap!$A$2:$B$19,2)</f>
-        <v>196652183.90000001</v>
+        <f>VLOOKUP(C39,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>217521514.44316691</v>
       </c>
       <c r="E39">
         <f t="shared" si="0"/>
-        <v>2505445.666201428</v>
+        <v>199037083.86320585</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B40">
-        <v>0.91502251799193601</v>
+        <v>5.9890161501362497E-2</v>
       </c>
       <c r="C40" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <f>VLOOKUP(C40,starting_cap!$A$2:$B$19,2)</f>
-        <v>138970173.69999999</v>
+        <f>VLOOKUP(C40,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>217521514.44316691</v>
       </c>
       <c r="E40">
         <f t="shared" si="0"/>
-        <v>127160838.26475072</v>
+        <v>13027398.630022222</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B41">
-        <v>5.9890161501362497E-2</v>
+        <v>2.5087320506701101E-2</v>
       </c>
       <c r="C41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <f>VLOOKUP(C41,starting_cap!$A$2:$B$19,2)</f>
-        <v>138970173.69999999</v>
+        <f>VLOOKUP(C41,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>217521514.44316691</v>
       </c>
       <c r="E41">
         <f t="shared" si="0"/>
-        <v>8322946.1467653988</v>
+        <v>5457031.9499387406</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42">
-        <v>2.5087320506701101E-2</v>
+        <v>0.352162617276225</v>
       </c>
       <c r="C42" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <f>VLOOKUP(C42,starting_cap!$A$2:$B$19,2)</f>
-        <v>138970173.69999999</v>
+        <f>VLOOKUP(C42,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>266622339.29579192</v>
       </c>
       <c r="E42">
         <f t="shared" si="0"/>
-        <v>3486389.2884838236</v>
+        <v>93894420.830715775</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B43">
-        <v>0.352162617276225</v>
+        <v>0.31873823734484802</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <f>VLOOKUP(C43,starting_cap!$A$2:$B$19,2)</f>
-        <v>188318801.59999999</v>
+        <f>VLOOKUP(C43,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>266622339.29579192</v>
       </c>
       <c r="E43">
         <f t="shared" si="0"/>
-        <v>66318842.053778149</v>
+        <v>84982734.46390073</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B44">
-        <v>0.31873823734484802</v>
+        <v>0.192155901226716</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44">
-        <f>VLOOKUP(C44,starting_cap!$A$2:$B$19,2)</f>
-        <v>188318801.59999999</v>
+        <f>VLOOKUP(C44,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>266622339.29579192</v>
       </c>
       <c r="E44">
         <f t="shared" si="0"/>
-        <v>60024402.880878143</v>
+        <v>51233055.894558154</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B45">
-        <v>0.192155901226716</v>
+        <v>0.13694324415220899</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <f>VLOOKUP(C45,starting_cap!$A$2:$B$19,2)</f>
-        <v>188318801.59999999</v>
+        <f>VLOOKUP(C45,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>266622339.29579192</v>
       </c>
       <c r="E45">
         <f t="shared" si="0"/>
-        <v>36186569.039383128</v>
+        <v>36512128.106616735</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>0.13694324415220899</v>
+        <v>0.590178760593704</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <f>VLOOKUP(C46,starting_cap!$A$2:$B$19,2)</f>
-        <v>188318801.59999999</v>
+        <f>VLOOKUP(C46,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>3172885.866301666</v>
       </c>
       <c r="E46">
         <f t="shared" si="0"/>
-        <v>25788987.625960205</v>
+        <v>1872569.848079198</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B47">
-        <v>0.590178760593704</v>
+        <v>0.17977648197656701</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <f>VLOOKUP(C47,starting_cap!$A$2:$B$19,2)</f>
-        <v>11549646.18</v>
+        <f>VLOOKUP(C47,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>3172885.866301666</v>
       </c>
       <c r="E47">
         <f t="shared" si="0"/>
-        <v>6816355.8678082079</v>
+        <v>570410.25875688565</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B48">
-        <v>0.17977648197656701</v>
+        <v>0.176380568497469</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <f>VLOOKUP(C48,starting_cap!$A$2:$B$19,2)</f>
-        <v>11549646.18</v>
+        <f>VLOOKUP(C48,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>3172885.866301666</v>
       </c>
       <c r="E48">
         <f t="shared" si="0"/>
-        <v>2076354.7583144959</v>
+        <v>559635.41287587222</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B49">
-        <v>0.176380568497469</v>
+        <v>5.3664188932258203E-2</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <f>VLOOKUP(C49,starting_cap!$A$2:$B$19,2)</f>
-        <v>11549646.18</v>
+        <f>VLOOKUP(C49,starting_cap!$A$2:$B$17,2,FALSE)</f>
+        <v>3172885.866301666</v>
       </c>
       <c r="E49">
         <f t="shared" si="0"/>
-        <v>2037133.1591730211</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50">
-        <v>5.3664188932258203E-2</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50">
-        <f>VLOOKUP(C50,starting_cap!$A$2:$B$19,2)</f>
-        <v>11549646.18</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="0"/>
-        <v>619802.39470425423</v>
+        <v>170270.34658970434</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E51" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}"/>
+  <autoFilter ref="A1:E50" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA/production_capacity_scenarios/cap_builder.xlsx
+++ b/DATA/production_capacity_scenarios/cap_builder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF4F9CE-542A-4F7A-9DCD-734FC4397F51}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F093489-6990-4AB0-8A55-24CDB159A350}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
@@ -698,10 +698,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1022,13 +1018,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA7A5DA-6C9D-46FC-975A-A9F5DD878FF9}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1044,7 +1040,7 @@
         <v>977251.31527214276</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1052,7 +1048,7 @@
         <v>13328055.520714156</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1060,7 +1056,7 @@
         <v>321326687.20403224</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1068,7 +1064,7 @@
         <v>6402511.719496578</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1076,7 +1072,7 @@
         <v>59151603.417757481</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1084,7 +1080,7 @@
         <v>277874999.07853091</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1092,7 +1088,7 @@
         <v>302888.81815348461</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1100,7 +1096,7 @@
         <v>6311801.7126107905</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1108,7 +1104,7 @@
         <v>66709612.957940787</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1116,7 +1112,7 @@
         <v>136545787.17132425</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +1120,7 @@
         <v>266622339.29579192</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1132,15 +1128,15 @@
         <v>3172885.866301666</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
       <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>438402962.04456699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1148,7 +1144,7 @@
         <v>35984585.712862946</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1156,7 +1152,7 @@
         <v>217521514.44316691</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1172,30 +1168,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1221,7 +1217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1236,18 +1232,18 @@
         <v>6402511.719496578</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E49" si="0">D2*B2</f>
+        <f>D2*B2</f>
         <v>3958786.3845079578</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J16" si="1">SUMIF(A:A, I2, E:E)</f>
+        <f t="shared" ref="J2:J16" si="0">SUMIF(A:A, I2, E:E)</f>
         <v>12102355.415715292</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1262,18 +1258,18 @@
         <v>6402511.719496578</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E2:E49" si="1">D3*B3</f>
         <v>2443725.3349886201</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>55762252.537822999</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1288,18 +1284,18 @@
         <v>59151603.417757481</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46967196.599250063</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
-        <v>5457031.9499387406</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>77986389.151167125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1314,18 +1310,18 @@
         <v>59151603.417757481</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12184406.818507425</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18909478.051597763</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1340,18 +1336,18 @@
         <v>6311801.7126107905</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6311801.7126107905</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>176656204.10945982</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1366,18 +1362,18 @@
         <v>66709612.957940787</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35030933.557310052</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
-        <v>1317354.7756154076</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>14503588.18448288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1392,18 +1388,18 @@
         <v>66709612.957940787</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31678679.400630668</v>
       </c>
       <c r="I8" t="s">
         <v>23</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>379834532.08035249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>414824585.3056196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1418,18 +1414,18 @@
         <v>302888.81815348461</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>302888.81815348461</v>
       </c>
       <c r="I9" t="s">
         <v>24</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>102061729.61303598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1444,18 +1440,18 @@
         <v>35984585.712862946</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31938848.527961027</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>89157748.448498234</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1470,18 +1466,18 @@
         <v>35984585.712862946</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2728382.4092865069</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31938848.527961027</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1496,18 +1492,18 @@
         <v>35984585.712862946</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1317354.7756154076</v>
       </c>
       <c r="I12" t="s">
         <v>27</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
-        <v>14015815.917442642</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>15219754.312615251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1522,18 +1518,18 @@
         <v>136545787.17132425</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>101436558.60119651</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>127439682.10564198</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1548,18 +1544,18 @@
         <v>136545787.17132425</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18909478.051597763</v>
       </c>
       <c r="I14" t="s">
         <v>28</v>
       </c>
       <c r="J14">
-        <f t="shared" si="1"/>
-        <v>42815576.129015923</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>56000384.381950192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1574,18 +1570,18 @@
         <v>136545787.17132425</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4097395.1028146716</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15">
-        <f t="shared" si="1"/>
-        <v>101739447.41935</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>130015283.84818706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1600,18 +1596,18 @@
         <v>136545787.17132425</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12102355.415715292</v>
       </c>
       <c r="I16" t="s">
         <v>29</v>
       </c>
       <c r="J16">
-        <f t="shared" si="1"/>
-        <v>581266772.68311989</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>754237778.20234299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1626,11 +1622,11 @@
         <v>977251.31527214276</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>828063.30500688718</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1645,11 +1641,11 @@
         <v>977251.31527214276</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>149188.01026525456</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1664,11 +1660,11 @@
         <v>321326687.20403224</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>235424959.37692702</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1683,11 +1679,11 @@
         <v>321326687.20403224</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>85901727.827104896</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1702,11 +1698,11 @@
         <v>13328055.520714156</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11211272.916422246</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1721,11 +1717,11 @@
         <v>13328055.520714156</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2116782.6042918968</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1737,14 +1733,14 @@
       </c>
       <c r="D23">
         <f>VLOOKUP(C23,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>172971005.51922327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1756,14 +1752,14 @@
       </c>
       <c r="D24">
         <f>VLOOKUP(C24,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>102061729.61303598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1775,14 +1771,14 @@
       </c>
       <c r="D25">
         <f>VLOOKUP(C25,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>72529357.20122838</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1794,14 +1790,14 @@
       </c>
       <c r="D26">
         <f>VLOOKUP(C26,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>34990053.22526715</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1813,14 +1809,14 @@
       </c>
       <c r="D27">
         <f>VLOOKUP(C27,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>28275836.428837061</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1832,14 +1828,14 @@
       </c>
       <c r="D28">
         <f>VLOOKUP(C28,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>13186233.408867473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1851,14 +1847,14 @@
       </c>
       <c r="D29">
         <f>VLOOKUP(C29,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>13184808.252934271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1870,14 +1866,14 @@
       </c>
       <c r="D30">
         <f>VLOOKUP(C30,starting_cap!$A$2:$B$17,2,FALSE)</f>
-        <v>0</v>
+        <v>438402962.04456699</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>1203938.3951726083</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1892,11 +1888,11 @@
         <v>226180575.91757733</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127439682.10564198</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -1911,11 +1907,11 @@
         <v>226180575.91757733</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>92167337.98075521</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1930,11 +1926,11 @@
         <v>226180575.91757733</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6573555.8311797418</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1949,11 +1945,11 @@
         <v>277874999.07853091</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>140349220.87761426</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -1968,11 +1964,11 @@
         <v>277874999.07853091</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66588024.007865503</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -1987,11 +1983,11 @@
         <v>277874999.07853091</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53381673.945052892</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -2006,11 +2002,11 @@
         <v>277874999.07853091</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14015815.917442642</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -2025,11 +2021,11 @@
         <v>277874999.07853091</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3540264.3305556043</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2044,11 +2040,11 @@
         <v>217521514.44316691</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>199037083.86320585</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -2063,11 +2059,11 @@
         <v>217521514.44316691</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13027398.630022222</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -2082,11 +2078,11 @@
         <v>217521514.44316691</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5457031.9499387406</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -2101,11 +2097,11 @@
         <v>266622339.29579192</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>93894420.830715775</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -2120,11 +2116,11 @@
         <v>266622339.29579192</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84982734.46390073</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2139,11 +2135,11 @@
         <v>266622339.29579192</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51233055.894558154</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -2158,11 +2154,11 @@
         <v>266622339.29579192</v>
       </c>
       <c r="E45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36512128.106616735</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2177,11 +2173,11 @@
         <v>3172885.866301666</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1872569.848079198</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -2196,11 +2192,11 @@
         <v>3172885.866301666</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>570410.25875688565</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -2215,11 +2211,11 @@
         <v>3172885.866301666</v>
       </c>
       <c r="E48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>559635.41287587222</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -2234,7 +2230,7 @@
         <v>3172885.866301666</v>
       </c>
       <c r="E49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>170270.34658970434</v>
       </c>
     </row>
